--- a/tracker/Travnook_TL_Tracker_Oct2026.xlsx
+++ b/tracker/Travnook_TL_Tracker_Oct2026.xlsx
@@ -58,6 +58,18 @@
         </r>
       </text>
     </comment>
+    <comment ref="N11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Number of lost deals not given. Enter the count.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="R9" authorId="0">
       <text>
         <r>
@@ -97,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="283">
   <si>
     <t xml:space="preserve">TEAM LEADER REPORT · FORM 1 OF 4 · KEEP ONE ROW PER WORKING DAY</t>
   </si>
@@ -223,6 +235,15 @@
   </si>
   <si>
     <t xml:space="preserve">Ibrahim and Layan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most - junk leads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM issue: old leads redirecting to agents.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL</t>
@@ -413,6 +434,9 @@
     <t xml:space="preserve">COMMENT</t>
   </si>
   <si>
+    <t xml:space="preserve">Most of them junk leads. Redirected leads from Moana to Saha and Khozema.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reason: PR Price too high · CM Chose competitor · NR No reply / went silent · TM Timing / not ready · BG Budget · NF Not a fit · PY Payment issue · OT Other</t>
   </si>
   <si>
@@ -483,6 +507,9 @@
   </si>
   <si>
     <t xml:space="preserve">Technical and network issues. Instagram and TikTok leads not captured as contact numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM</t>
   </si>
   <si>
     <t xml:space="preserve">System: BOT Chat App Bot · CRM CRM · DB Dashboard · LD Leads     Impact: B Blocking sales · S Slowing work · M Minor     Status: O Open · F Fixed</t>
@@ -3415,21 +3442,45 @@
         <f aca="false">IF(A11="","",IF(OR(WEEKDAY(A11,2)=7,COUNTIF('4 Monthly Review'!$B$26:$AM$26,A11)&gt;0),0,1))</f>
         <v>1</v>
       </c>
-      <c r="E11" s="16"/>
-      <c r="F11" s="16"/>
+      <c r="E11" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>3</v>
+      </c>
       <c r="G11" s="18"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="16"/>
+      <c r="H11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="K11" s="19"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="16"/>
+      <c r="L11" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="O11" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="18"/>
+      <c r="Q11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="18" t="s">
+        <v>44</v>
+      </c>
       <c r="T11" s="18"/>
       <c r="U11" s="20"/>
       <c r="V11" s="20"/>
@@ -4966,23 +5017,23 @@
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B40" s="24"/>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" s="25" t="n">
         <f aca="false">SUM(E9:E39)</f>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F40" s="25" t="n">
         <f aca="false">SUM(F9:F39)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G40" s="26"/>
       <c r="H40" s="25" t="n">
         <f aca="false">SUM(H9:H39)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="25" t="n">
@@ -5013,7 +5064,7 @@
       </c>
       <c r="R40" s="25" t="n">
         <f aca="false">SUM(R9:R39)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S40" s="26"/>
       <c r="T40" s="26"/>
@@ -5152,7 +5203,7 @@
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2"/>
       <c r="C2" s="28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
@@ -5198,7 +5249,7 @@
       <c r="AS2" s="2"/>
       <c r="AT2" s="2"/>
       <c r="AU2" s="29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AV2" s="29"/>
       <c r="AW2" s="29"/>
@@ -5212,7 +5263,7 @@
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2"/>
       <c r="C3" s="30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -5255,7 +5306,7 @@
       <c r="AP3" s="30"/>
       <c r="AQ3" s="30"/>
       <c r="AR3" s="31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AS3" s="31"/>
       <c r="AT3" s="31"/>
@@ -5272,7 +5323,7 @@
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2"/>
       <c r="C4" s="32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
@@ -5442,7 +5493,7 @@
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
@@ -5475,7 +5526,7 @@
       <c r="AD8" s="33"/>
       <c r="AE8" s="33"/>
       <c r="AG8" s="33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="AH8" s="33"/>
       <c r="AI8" s="33"/>
@@ -5488,7 +5539,7 @@
       <c r="AP8" s="33"/>
       <c r="AQ8" s="33"/>
       <c r="AS8" s="33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AT8" s="33"/>
       <c r="AU8" s="33"/>
@@ -5629,7 +5680,7 @@
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6"/>
       <c r="C13" s="37" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37"/>
@@ -5660,7 +5711,7 @@
       <c r="AD13" s="37"/>
       <c r="AE13" s="37"/>
       <c r="AF13" s="38" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AG13" s="38"/>
       <c r="AH13" s="38"/>
@@ -5689,7 +5740,7 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="39"/>
       <c r="C14" s="40" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" s="40"/>
       <c r="E14" s="40"/>
@@ -5704,7 +5755,7 @@
       <c r="N14" s="41"/>
       <c r="P14" s="39"/>
       <c r="Q14" s="40" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="R14" s="40"/>
       <c r="S14" s="40"/>
@@ -5719,7 +5770,7 @@
       <c r="AB14" s="41"/>
       <c r="AD14" s="39"/>
       <c r="AE14" s="40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AF14" s="40"/>
       <c r="AG14" s="40"/>
@@ -5734,7 +5785,7 @@
       <c r="AP14" s="41"/>
       <c r="AR14" s="39"/>
       <c r="AS14" s="40" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AT14" s="40"/>
       <c r="AU14" s="40"/>
@@ -5750,7 +5801,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="42"/>
       <c r="C15" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" s="43"/>
       <c r="E15" s="43"/>
@@ -5765,7 +5816,7 @@
       <c r="N15" s="44"/>
       <c r="P15" s="42"/>
       <c r="Q15" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R15" s="43"/>
       <c r="S15" s="43"/>
@@ -5780,7 +5831,7 @@
       <c r="AB15" s="44"/>
       <c r="AD15" s="42"/>
       <c r="AE15" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AF15" s="43"/>
       <c r="AG15" s="43"/>
@@ -5795,7 +5846,7 @@
       <c r="AP15" s="44"/>
       <c r="AR15" s="42"/>
       <c r="AS15" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AT15" s="43"/>
       <c r="AU15" s="43"/>
@@ -5803,7 +5854,7 @@
       <c r="AW15" s="43"/>
       <c r="AX15" s="45"/>
       <c r="AY15" s="43" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="AZ15" s="43"/>
       <c r="BA15" s="43"/>
@@ -5814,7 +5865,7 @@
       <c r="B16" s="42"/>
       <c r="C16" s="46" t="n">
         <f aca="false">IFERROR(SUMIFS('1 Daily Report'!$F$9:$F$39,'1 Daily Report'!$A$9:$A$39,"&gt;="&amp;INDEX('4 Monthly Review'!$F$18:$F$22,'3 Weekly Report'!$H$2),'1 Daily Report'!$A$9:$A$39,"&lt;="&amp;INDEX('4 Monthly Review'!$K$18:$K$22,'3 Weekly Report'!$H$2)),0)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="46"/>
       <c r="E16" s="46"/>
@@ -5830,7 +5881,7 @@
       <c r="P16" s="42"/>
       <c r="Q16" s="46" t="n">
         <f aca="false">IFERROR(SUMIFS('1 Daily Report'!$H$9:$H$39,'1 Daily Report'!$A$9:$A$39,"&gt;="&amp;INDEX('4 Monthly Review'!$F$18:$F$22,'3 Weekly Report'!$H$2),'1 Daily Report'!$A$9:$A$39,"&lt;="&amp;INDEX('4 Monthly Review'!$K$18:$K$22,'3 Weekly Report'!$H$2)),0)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R16" s="46"/>
       <c r="S16" s="46"/>
@@ -5935,7 +5986,7 @@
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="39"/>
       <c r="C19" s="40" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D19" s="40"/>
       <c r="E19" s="40"/>
@@ -5950,7 +6001,7 @@
       <c r="N19" s="41"/>
       <c r="P19" s="39"/>
       <c r="Q19" s="40" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="R19" s="40"/>
       <c r="S19" s="40"/>
@@ -5965,7 +6016,7 @@
       <c r="AB19" s="41"/>
       <c r="AD19" s="39"/>
       <c r="AE19" s="40" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="AF19" s="40"/>
       <c r="AG19" s="40"/>
@@ -5980,7 +6031,7 @@
       <c r="AP19" s="41"/>
       <c r="AR19" s="39"/>
       <c r="AS19" s="40" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="AT19" s="40"/>
       <c r="AU19" s="40"/>
@@ -5996,7 +6047,7 @@
     <row r="20" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="42"/>
       <c r="C20" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
@@ -6004,7 +6055,7 @@
       <c r="G20" s="43"/>
       <c r="H20" s="45"/>
       <c r="I20" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J20" s="43"/>
       <c r="K20" s="43"/>
@@ -6013,7 +6064,7 @@
       <c r="N20" s="44"/>
       <c r="P20" s="42"/>
       <c r="Q20" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="R20" s="43"/>
       <c r="S20" s="43"/>
@@ -6021,7 +6072,7 @@
       <c r="U20" s="43"/>
       <c r="V20" s="45"/>
       <c r="W20" s="43" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="X20" s="43"/>
       <c r="Y20" s="43"/>
@@ -6030,7 +6081,7 @@
       <c r="AB20" s="44"/>
       <c r="AD20" s="42"/>
       <c r="AE20" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AF20" s="43"/>
       <c r="AG20" s="43"/>
@@ -6038,7 +6089,7 @@
       <c r="AI20" s="43"/>
       <c r="AJ20" s="45"/>
       <c r="AK20" s="43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="AL20" s="43"/>
       <c r="AM20" s="43"/>
@@ -6047,7 +6098,7 @@
       <c r="AP20" s="44"/>
       <c r="AR20" s="42"/>
       <c r="AS20" s="43" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AT20" s="43"/>
       <c r="AU20" s="43"/>
@@ -6102,7 +6153,7 @@
       <c r="AD21" s="42"/>
       <c r="AE21" s="46" t="n">
         <f aca="false">IFERROR(SUMIFS('1 Daily Report'!$R$9:$R$39,'1 Daily Report'!$A$9:$A$39,"&gt;="&amp;INDEX('4 Monthly Review'!$F$18:$F$22,'3 Weekly Report'!$H$2),'1 Daily Report'!$A$9:$A$39,"&lt;="&amp;INDEX('4 Monthly Review'!$K$18:$K$22,'3 Weekly Report'!$H$2)),0)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF21" s="46"/>
       <c r="AG21" s="46"/>
@@ -6191,7 +6242,7 @@
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="6"/>
       <c r="C24" s="51" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D24" s="51"/>
       <c r="E24" s="51"/>
@@ -6305,7 +6356,7 @@
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6"/>
       <c r="C28" s="37" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="37"/>
@@ -6342,7 +6393,7 @@
       <c r="AJ28" s="37"/>
       <c r="AK28" s="37"/>
       <c r="AL28" s="38" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="AM28" s="38"/>
       <c r="AN28" s="38"/>
@@ -6364,17 +6415,17 @@
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C29" s="52"/>
       <c r="D29" s="53" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E29" s="53"/>
       <c r="F29" s="53"/>
       <c r="G29" s="53"/>
       <c r="H29" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
@@ -6383,7 +6434,7 @@
       <c r="M29" s="53"/>
       <c r="N29" s="53"/>
       <c r="O29" s="53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P29" s="53"/>
       <c r="Q29" s="53"/>
@@ -6392,13 +6443,13 @@
       <c r="T29" s="53"/>
       <c r="U29" s="53"/>
       <c r="V29" s="53" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W29" s="53"/>
       <c r="X29" s="53"/>
       <c r="Y29" s="53"/>
       <c r="Z29" s="53" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="AA29" s="53"/>
       <c r="AB29" s="53"/>
@@ -6460,7 +6511,7 @@
       <c r="X30" s="56"/>
       <c r="Y30" s="56"/>
       <c r="Z30" s="56" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AA30" s="56"/>
       <c r="AB30" s="56"/>
@@ -12240,11 +12291,11 @@
     </row>
     <row r="130" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B130" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C130" s="57"/>
       <c r="E130" s="58" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F130" s="58"/>
       <c r="G130" s="58"/>
@@ -12301,7 +12352,7 @@
     <row r="132" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B132" s="6"/>
       <c r="C132" s="37" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D132" s="37"/>
       <c r="E132" s="37"/>
@@ -12338,7 +12389,7 @@
       <c r="AJ132" s="37"/>
       <c r="AK132" s="37"/>
       <c r="AL132" s="38" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="AM132" s="38"/>
       <c r="AN132" s="38"/>
@@ -12360,7 +12411,7 @@
     </row>
     <row r="133" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C133" s="52"/>
       <c r="D133" s="53" t="s">
@@ -12370,7 +12421,7 @@
       <c r="F133" s="53"/>
       <c r="G133" s="53"/>
       <c r="H133" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I133" s="53"/>
       <c r="J133" s="53"/>
@@ -12380,13 +12431,13 @@
       <c r="N133" s="53"/>
       <c r="O133" s="53"/>
       <c r="P133" s="53" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="Q133" s="53"/>
       <c r="R133" s="53"/>
       <c r="S133" s="53"/>
       <c r="T133" s="53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U133" s="53"/>
       <c r="V133" s="53"/>
@@ -12408,7 +12459,7 @@
       <c r="AL133" s="53"/>
       <c r="AM133" s="53"/>
       <c r="AN133" s="53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="AO133" s="53"/>
       <c r="AP133" s="53"/>
@@ -12438,7 +12489,7 @@
       <c r="F134" s="55"/>
       <c r="G134" s="55"/>
       <c r="H134" s="56" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I134" s="56"/>
       <c r="J134" s="56"/>
@@ -12500,7 +12551,7 @@
       <c r="F135" s="55"/>
       <c r="G135" s="55"/>
       <c r="H135" s="56" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I135" s="56"/>
       <c r="J135" s="56"/>
@@ -12562,7 +12613,7 @@
       <c r="F136" s="55"/>
       <c r="G136" s="55"/>
       <c r="H136" s="56" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I136" s="56"/>
       <c r="J136" s="56"/>
@@ -12624,7 +12675,7 @@
       <c r="F137" s="55"/>
       <c r="G137" s="55"/>
       <c r="H137" s="56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I137" s="56"/>
       <c r="J137" s="56"/>
@@ -12679,11 +12730,15 @@
         <v>5</v>
       </c>
       <c r="C138" s="54"/>
-      <c r="D138" s="55"/>
+      <c r="D138" s="55" t="n">
+        <v>46298</v>
+      </c>
       <c r="E138" s="55"/>
       <c r="F138" s="55"/>
       <c r="G138" s="55"/>
-      <c r="H138" s="56"/>
+      <c r="H138" s="56" t="s">
+        <v>85</v>
+      </c>
       <c r="I138" s="56"/>
       <c r="J138" s="56"/>
       <c r="K138" s="56"/>
@@ -12737,11 +12792,15 @@
         <v>6</v>
       </c>
       <c r="C139" s="54"/>
-      <c r="D139" s="55"/>
+      <c r="D139" s="55" t="n">
+        <v>46298</v>
+      </c>
       <c r="E139" s="55"/>
       <c r="F139" s="55"/>
       <c r="G139" s="55"/>
-      <c r="H139" s="56"/>
+      <c r="H139" s="56" t="s">
+        <v>86</v>
+      </c>
       <c r="I139" s="56"/>
       <c r="J139" s="56"/>
       <c r="K139" s="56"/>
@@ -17084,11 +17143,11 @@
     </row>
     <row r="214" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B214" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C214" s="57"/>
       <c r="E214" s="58" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F214" s="58"/>
       <c r="G214" s="58"/>
@@ -17145,7 +17204,7 @@
     <row r="216" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B216" s="6"/>
       <c r="C216" s="37" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D216" s="37"/>
       <c r="E216" s="37"/>
@@ -17182,7 +17241,7 @@
       <c r="AJ216" s="37"/>
       <c r="AK216" s="37"/>
       <c r="AL216" s="38" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AM216" s="38"/>
       <c r="AN216" s="38"/>
@@ -17204,7 +17263,7 @@
     </row>
     <row r="217" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B217" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C217" s="52"/>
       <c r="D217" s="53" t="s">
@@ -17214,7 +17273,7 @@
       <c r="F217" s="53"/>
       <c r="G217" s="53"/>
       <c r="H217" s="53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I217" s="53"/>
       <c r="J217" s="53"/>
@@ -17224,7 +17283,7 @@
       <c r="N217" s="53"/>
       <c r="O217" s="53"/>
       <c r="P217" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q217" s="53"/>
       <c r="R217" s="53"/>
@@ -17233,7 +17292,7 @@
       <c r="U217" s="53"/>
       <c r="V217" s="53"/>
       <c r="W217" s="53" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="X217" s="53"/>
       <c r="Y217" s="53"/>
@@ -17241,13 +17300,13 @@
       <c r="AA217" s="53"/>
       <c r="AB217" s="53"/>
       <c r="AC217" s="53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AD217" s="53"/>
       <c r="AE217" s="53"/>
       <c r="AF217" s="53"/>
       <c r="AG217" s="53" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AH217" s="53"/>
       <c r="AI217" s="53"/>
@@ -17277,7 +17336,9 @@
         <v>1</v>
       </c>
       <c r="C218" s="54"/>
-      <c r="D218" s="55"/>
+      <c r="D218" s="55" t="n">
+        <v>46298</v>
+      </c>
       <c r="E218" s="55"/>
       <c r="F218" s="55"/>
       <c r="G218" s="55"/>
@@ -17306,7 +17367,9 @@
       <c r="AD218" s="56"/>
       <c r="AE218" s="56"/>
       <c r="AF218" s="56"/>
-      <c r="AG218" s="56"/>
+      <c r="AG218" s="56" t="s">
+        <v>94</v>
+      </c>
       <c r="AH218" s="56"/>
       <c r="AI218" s="56"/>
       <c r="AJ218" s="56"/>
@@ -31774,11 +31837,11 @@
     </row>
     <row r="468" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B468" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C468" s="57"/>
       <c r="E468" s="58" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F468" s="58"/>
       <c r="G468" s="58"/>
@@ -31835,7 +31898,7 @@
     <row r="470" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B470" s="6"/>
       <c r="C470" s="37" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D470" s="37"/>
       <c r="E470" s="37"/>
@@ -31872,7 +31935,7 @@
       <c r="AJ470" s="37"/>
       <c r="AK470" s="37"/>
       <c r="AL470" s="38" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="AM470" s="38"/>
       <c r="AN470" s="38"/>
@@ -31894,7 +31957,7 @@
     </row>
     <row r="471" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B471" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C471" s="52"/>
       <c r="D471" s="53" t="s">
@@ -31904,7 +31967,7 @@
       <c r="F471" s="53"/>
       <c r="G471" s="53"/>
       <c r="H471" s="53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I471" s="53"/>
       <c r="J471" s="53"/>
@@ -31914,7 +31977,7 @@
       <c r="N471" s="53"/>
       <c r="O471" s="53"/>
       <c r="P471" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="Q471" s="53"/>
       <c r="R471" s="53"/>
@@ -31923,7 +31986,7 @@
       <c r="U471" s="53"/>
       <c r="V471" s="53"/>
       <c r="W471" s="53" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="X471" s="53"/>
       <c r="Y471" s="53"/>
@@ -31931,13 +31994,13 @@
       <c r="AA471" s="53"/>
       <c r="AB471" s="53"/>
       <c r="AC471" s="53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AD471" s="53"/>
       <c r="AE471" s="53"/>
       <c r="AF471" s="53"/>
       <c r="AG471" s="53" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AH471" s="53"/>
       <c r="AI471" s="53"/>
@@ -34284,11 +34347,11 @@
     </row>
     <row r="512" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B512" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C512" s="57"/>
       <c r="E512" s="58" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F512" s="58"/>
       <c r="G512" s="58"/>
@@ -34345,7 +34408,7 @@
     <row r="514" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B514" s="6"/>
       <c r="C514" s="37" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D514" s="37"/>
       <c r="E514" s="37"/>
@@ -34382,7 +34445,7 @@
       <c r="AJ514" s="37"/>
       <c r="AK514" s="37"/>
       <c r="AL514" s="38" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="AM514" s="38"/>
       <c r="AN514" s="38"/>
@@ -34404,7 +34467,7 @@
     </row>
     <row r="515" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B515" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C515" s="52"/>
       <c r="D515" s="53" t="s">
@@ -34414,7 +34477,7 @@
       <c r="F515" s="53"/>
       <c r="G515" s="53"/>
       <c r="H515" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I515" s="53"/>
       <c r="J515" s="53"/>
@@ -34423,7 +34486,7 @@
       <c r="M515" s="53"/>
       <c r="N515" s="53"/>
       <c r="O515" s="53" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="P515" s="53"/>
       <c r="Q515" s="53"/>
@@ -34441,13 +34504,13 @@
       <c r="AC515" s="53"/>
       <c r="AD515" s="53"/>
       <c r="AE515" s="53" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="AF515" s="53"/>
       <c r="AG515" s="53"/>
       <c r="AH515" s="53"/>
       <c r="AI515" s="53" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="AJ515" s="53"/>
       <c r="AK515" s="53"/>
@@ -34463,7 +34526,7 @@
       <c r="AU515" s="53"/>
       <c r="AV515" s="53"/>
       <c r="AW515" s="53" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AX515" s="53"/>
       <c r="AY515" s="53"/>
@@ -36794,11 +36857,11 @@
     </row>
     <row r="556" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B556" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C556" s="57"/>
       <c r="E556" s="58" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F556" s="58"/>
       <c r="G556" s="58"/>
@@ -36855,7 +36918,7 @@
     <row r="558" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B558" s="6"/>
       <c r="C558" s="37" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D558" s="37"/>
       <c r="E558" s="37"/>
@@ -36892,7 +36955,7 @@
       <c r="AJ558" s="37"/>
       <c r="AK558" s="37"/>
       <c r="AL558" s="38" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AM558" s="38"/>
       <c r="AN558" s="38"/>
@@ -36914,7 +36977,7 @@
     </row>
     <row r="559" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B559" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C559" s="52"/>
       <c r="D559" s="53" t="s">
@@ -36924,7 +36987,7 @@
       <c r="F559" s="53"/>
       <c r="G559" s="53"/>
       <c r="H559" s="53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I559" s="53"/>
       <c r="J559" s="53"/>
@@ -36935,7 +36998,7 @@
       <c r="O559" s="53"/>
       <c r="P559" s="53"/>
       <c r="Q559" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R559" s="53"/>
       <c r="S559" s="53"/>
@@ -36944,27 +37007,27 @@
       <c r="V559" s="53"/>
       <c r="W559" s="53"/>
       <c r="X559" s="53" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="Y559" s="53"/>
       <c r="Z559" s="53"/>
       <c r="AA559" s="53"/>
       <c r="AB559" s="53"/>
       <c r="AC559" s="53" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="AD559" s="53"/>
       <c r="AE559" s="53"/>
       <c r="AF559" s="53"/>
       <c r="AG559" s="53"/>
       <c r="AH559" s="53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="AI559" s="53"/>
       <c r="AJ559" s="53"/>
       <c r="AK559" s="53"/>
       <c r="AL559" s="53" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="AM559" s="53"/>
       <c r="AN559" s="53"/>
@@ -39306,11 +39369,11 @@
     </row>
     <row r="600" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B600" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C600" s="57"/>
       <c r="E600" s="58" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F600" s="58"/>
       <c r="G600" s="58"/>
@@ -39367,7 +39430,7 @@
     <row r="602" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B602" s="6"/>
       <c r="C602" s="37" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D602" s="37"/>
       <c r="E602" s="37"/>
@@ -39404,7 +39467,7 @@
       <c r="AJ602" s="37"/>
       <c r="AK602" s="37"/>
       <c r="AL602" s="38" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AM602" s="38"/>
       <c r="AN602" s="38"/>
@@ -39426,7 +39489,7 @@
     </row>
     <row r="603" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B603" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C603" s="52"/>
       <c r="D603" s="53" t="s">
@@ -39436,13 +39499,13 @@
       <c r="F603" s="53"/>
       <c r="G603" s="53"/>
       <c r="H603" s="53" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="I603" s="53"/>
       <c r="J603" s="53"/>
       <c r="K603" s="53"/>
       <c r="L603" s="53" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="M603" s="53"/>
       <c r="N603" s="53"/>
@@ -39466,13 +39529,13 @@
       <c r="AF603" s="53"/>
       <c r="AG603" s="53"/>
       <c r="AH603" s="53" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AI603" s="53"/>
       <c r="AJ603" s="53"/>
       <c r="AK603" s="53"/>
       <c r="AL603" s="53" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AM603" s="53"/>
       <c r="AN603" s="53"/>
@@ -39484,7 +39547,7 @@
       <c r="AT603" s="53"/>
       <c r="AU603" s="53"/>
       <c r="AV603" s="53" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AW603" s="53"/>
       <c r="AX603" s="53"/>
@@ -39510,7 +39573,7 @@
       <c r="J604" s="56"/>
       <c r="K604" s="56"/>
       <c r="L604" s="56" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="M604" s="56"/>
       <c r="N604" s="56"/>
@@ -39561,15 +39624,21 @@
         <v>2</v>
       </c>
       <c r="C605" s="54"/>
-      <c r="D605" s="55"/>
+      <c r="D605" s="55" t="n">
+        <v>46298</v>
+      </c>
       <c r="E605" s="55"/>
       <c r="F605" s="55"/>
       <c r="G605" s="55"/>
-      <c r="H605" s="56"/>
+      <c r="H605" s="56" t="s">
+        <v>119</v>
+      </c>
       <c r="I605" s="56"/>
       <c r="J605" s="56"/>
       <c r="K605" s="56"/>
-      <c r="L605" s="56"/>
+      <c r="L605" s="56" t="s">
+        <v>44</v>
+      </c>
       <c r="M605" s="56"/>
       <c r="N605" s="56"/>
       <c r="O605" s="56"/>
@@ -41820,11 +41889,11 @@
     </row>
     <row r="644" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B644" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C644" s="57"/>
       <c r="E644" s="58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F644" s="58"/>
       <c r="G644" s="58"/>
@@ -41881,7 +41950,7 @@
     <row r="646" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B646" s="6"/>
       <c r="C646" s="37" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D646" s="37"/>
       <c r="E646" s="37"/>
@@ -41918,7 +41987,7 @@
       <c r="AJ646" s="37"/>
       <c r="AK646" s="37"/>
       <c r="AL646" s="38" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="AM646" s="38"/>
       <c r="AN646" s="38"/>
@@ -41940,7 +42009,7 @@
     </row>
     <row r="647" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B647" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C647" s="52"/>
       <c r="D647" s="53" t="s">
@@ -41950,7 +42019,7 @@
       <c r="F647" s="53"/>
       <c r="G647" s="53"/>
       <c r="H647" s="53" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I647" s="53"/>
       <c r="J647" s="53"/>
@@ -41960,13 +42029,13 @@
       <c r="N647" s="53"/>
       <c r="O647" s="53"/>
       <c r="P647" s="53" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="Q647" s="53"/>
       <c r="R647" s="53"/>
       <c r="S647" s="53"/>
       <c r="T647" s="53" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="U647" s="53"/>
       <c r="V647" s="53"/>
@@ -41980,7 +42049,7 @@
       <c r="AD647" s="53"/>
       <c r="AE647" s="53"/>
       <c r="AF647" s="53" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="AG647" s="53"/>
       <c r="AH647" s="53"/>
@@ -42092,7 +42161,7 @@
       <c r="N649" s="56"/>
       <c r="O649" s="56"/>
       <c r="P649" s="56" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="Q649" s="56"/>
       <c r="R649" s="56"/>
@@ -42139,11 +42208,15 @@
         <v>3</v>
       </c>
       <c r="C650" s="54"/>
-      <c r="D650" s="55"/>
+      <c r="D650" s="55" t="n">
+        <v>46298</v>
+      </c>
       <c r="E650" s="55"/>
       <c r="F650" s="55"/>
       <c r="G650" s="55"/>
-      <c r="H650" s="56"/>
+      <c r="H650" s="56" t="s">
+        <v>42</v>
+      </c>
       <c r="I650" s="56"/>
       <c r="J650" s="56"/>
       <c r="K650" s="56"/>
@@ -42151,7 +42224,9 @@
       <c r="M650" s="56"/>
       <c r="N650" s="56"/>
       <c r="O650" s="56"/>
-      <c r="P650" s="56"/>
+      <c r="P650" s="56" t="n">
+        <v>0</v>
+      </c>
       <c r="Q650" s="56"/>
       <c r="R650" s="56"/>
       <c r="S650" s="56"/>
@@ -44340,11 +44415,11 @@
     </row>
     <row r="688" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B688" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C688" s="57"/>
       <c r="E688" s="58" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="F688" s="58"/>
       <c r="G688" s="58"/>
@@ -44401,7 +44476,7 @@
     <row r="690" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B690" s="6"/>
       <c r="C690" s="37" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D690" s="37"/>
       <c r="E690" s="37"/>
@@ -44438,7 +44513,7 @@
       <c r="AJ690" s="37"/>
       <c r="AK690" s="37"/>
       <c r="AL690" s="38" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="AM690" s="38"/>
       <c r="AN690" s="38"/>
@@ -44460,11 +44535,11 @@
     </row>
     <row r="691" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B691" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C691" s="52"/>
       <c r="D691" s="53" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E691" s="53"/>
       <c r="F691" s="53"/>
@@ -44475,7 +44550,7 @@
       <c r="K691" s="53"/>
       <c r="L691" s="53"/>
       <c r="M691" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N691" s="53"/>
       <c r="O691" s="53"/>
@@ -44485,7 +44560,7 @@
       <c r="S691" s="53"/>
       <c r="T691" s="53"/>
       <c r="U691" s="53" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="V691" s="53"/>
       <c r="W691" s="53"/>
@@ -44510,7 +44585,7 @@
       <c r="AP691" s="53"/>
       <c r="AQ691" s="53"/>
       <c r="AR691" s="53" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="AS691" s="53"/>
       <c r="AT691" s="53"/>
@@ -44520,7 +44595,7 @@
       <c r="AX691" s="53"/>
       <c r="AY691" s="53"/>
       <c r="AZ691" s="53" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="BA691" s="53"/>
       <c r="BB691" s="53"/>
@@ -48010,7 +48085,7 @@
     <row r="753" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B753" s="6"/>
       <c r="C753" s="37" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D753" s="37"/>
       <c r="E753" s="37"/>
@@ -48047,7 +48122,7 @@
       <c r="AJ753" s="37"/>
       <c r="AK753" s="37"/>
       <c r="AL753" s="38" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="AM753" s="38"/>
       <c r="AN753" s="38"/>
@@ -48069,11 +48144,11 @@
     </row>
     <row r="754" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B754" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C754" s="52"/>
       <c r="D754" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E754" s="53"/>
       <c r="F754" s="53"/>
@@ -48084,7 +48159,7 @@
       <c r="K754" s="53"/>
       <c r="L754" s="53"/>
       <c r="M754" s="53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="N754" s="53"/>
       <c r="O754" s="53"/>
@@ -48098,7 +48173,7 @@
       <c r="W754" s="53"/>
       <c r="X754" s="53"/>
       <c r="Y754" s="53" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="Z754" s="53"/>
       <c r="AA754" s="53"/>
@@ -48117,7 +48192,7 @@
       <c r="AN754" s="53"/>
       <c r="AO754" s="53"/>
       <c r="AP754" s="53" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="AQ754" s="53"/>
       <c r="AR754" s="53"/>
@@ -50457,7 +50532,7 @@
     <row r="796" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B796" s="6"/>
       <c r="C796" s="37" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D796" s="37"/>
       <c r="E796" s="37"/>
@@ -50494,7 +50569,7 @@
       <c r="AJ796" s="37"/>
       <c r="AK796" s="37"/>
       <c r="AL796" s="38" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AM796" s="38"/>
       <c r="AN796" s="38"/>
@@ -50516,7 +50591,7 @@
     </row>
     <row r="797" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B797" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C797" s="52"/>
       <c r="D797" s="53" t="s">
@@ -50526,7 +50601,7 @@
       <c r="F797" s="53"/>
       <c r="G797" s="53"/>
       <c r="H797" s="53" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I797" s="53"/>
       <c r="J797" s="53"/>
@@ -50537,7 +50612,7 @@
       <c r="O797" s="53"/>
       <c r="P797" s="53"/>
       <c r="Q797" s="53" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="R797" s="53"/>
       <c r="S797" s="53"/>
@@ -50545,7 +50620,7 @@
       <c r="U797" s="53"/>
       <c r="V797" s="53"/>
       <c r="W797" s="53" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="X797" s="53"/>
       <c r="Y797" s="53"/>
@@ -52902,11 +52977,11 @@
     </row>
     <row r="838" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B838" s="57" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C838" s="57"/>
       <c r="E838" s="58" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F838" s="58"/>
       <c r="G838" s="58"/>
@@ -58225,7 +58300,7 @@
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="60"/>
       <c r="C2" s="61" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -58313,7 +58388,7 @@
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="2"/>
       <c r="C5" s="28" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="D5" s="28"/>
       <c r="E5" s="28"/>
@@ -58343,7 +58418,7 @@
       <c r="AC5" s="2"/>
       <c r="AD5" s="2"/>
       <c r="AE5" s="29" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="AF5" s="29"/>
       <c r="AG5" s="29"/>
@@ -58357,7 +58432,7 @@
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="2"/>
       <c r="C6" s="30" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="D6" s="30"/>
       <c r="E6" s="30"/>
@@ -58384,7 +58459,7 @@
       <c r="Z6" s="30"/>
       <c r="AA6" s="30"/>
       <c r="AB6" s="31" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="AC6" s="31"/>
       <c r="AD6" s="31"/>
@@ -58401,7 +58476,7 @@
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="2"/>
       <c r="C7" s="32" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D7" s="32"/>
       <c r="E7" s="32"/>
@@ -58523,7 +58598,7 @@
     <row r="10" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
@@ -58547,7 +58622,7 @@
       <c r="U11" s="33"/>
       <c r="V11" s="33"/>
       <c r="X11" s="33" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Y11" s="33"/>
       <c r="Z11" s="33"/>
@@ -58557,7 +58632,7 @@
       <c r="AD11" s="33"/>
       <c r="AE11" s="33"/>
       <c r="AG11" s="33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AH11" s="33"/>
       <c r="AI11" s="33"/>
@@ -58619,7 +58694,7 @@
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6"/>
       <c r="C14" s="37" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="37"/>
@@ -58664,7 +58739,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="65" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E15" s="65"/>
       <c r="F15" s="65"/>
@@ -58680,7 +58755,7 @@
         <v>2</v>
       </c>
       <c r="Q15" s="65" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="R15" s="65"/>
       <c r="S15" s="65"/>
@@ -58696,7 +58771,7 @@
         <v>3</v>
       </c>
       <c r="AD15" s="65" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AE15" s="65"/>
       <c r="AF15" s="65"/>
@@ -58797,7 +58872,7 @@
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="6"/>
       <c r="C19" s="37" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D19" s="37"/>
       <c r="E19" s="37"/>
@@ -58838,11 +58913,11 @@
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="52" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C20" s="52"/>
       <c r="D20" s="53" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
@@ -58858,7 +58933,7 @@
       <c r="P20" s="53"/>
       <c r="Q20" s="53"/>
       <c r="R20" s="53" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="S20" s="53"/>
       <c r="T20" s="53"/>
@@ -58868,7 +58943,7 @@
       <c r="X20" s="53"/>
       <c r="Y20" s="53"/>
       <c r="Z20" s="53" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AA20" s="53"/>
       <c r="AB20" s="53"/>
@@ -58878,7 +58953,7 @@
       <c r="AF20" s="53"/>
       <c r="AG20" s="53"/>
       <c r="AH20" s="53" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AI20" s="53"/>
       <c r="AJ20" s="53"/>
@@ -59364,7 +59439,7 @@
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6"/>
       <c r="C31" s="37" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="37"/>
@@ -59373,7 +59448,7 @@
       <c r="H31" s="37"/>
       <c r="I31" s="37"/>
       <c r="J31" s="38" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K31" s="38"/>
       <c r="L31" s="38"/>
@@ -59384,7 +59459,7 @@
       <c r="Q31" s="38"/>
       <c r="S31" s="6"/>
       <c r="T31" s="37" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="U31" s="37"/>
       <c r="V31" s="37"/>
@@ -59392,7 +59467,7 @@
       <c r="X31" s="37"/>
       <c r="Y31" s="37"/>
       <c r="Z31" s="38" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AA31" s="38"/>
       <c r="AB31" s="38"/>
@@ -59414,7 +59489,7 @@
         <v>4</v>
       </c>
       <c r="D32" s="65" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E32" s="65"/>
       <c r="F32" s="65"/>
@@ -59426,7 +59501,7 @@
         <v>5</v>
       </c>
       <c r="M32" s="65" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="N32" s="65"/>
       <c r="O32" s="65"/>
@@ -59437,7 +59512,7 @@
         <v>6</v>
       </c>
       <c r="U32" s="65" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="V32" s="65"/>
       <c r="W32" s="65"/>
@@ -59448,7 +59523,7 @@
         <v>7</v>
       </c>
       <c r="AC32" s="65" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="AD32" s="65"/>
       <c r="AE32" s="65"/>
@@ -59458,7 +59533,7 @@
         <v>8</v>
       </c>
       <c r="AJ32" s="65" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="AK32" s="65"/>
       <c r="AL32" s="65"/>
@@ -59555,7 +59630,7 @@
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="6"/>
       <c r="C36" s="37" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D36" s="37"/>
       <c r="E36" s="37"/>
@@ -59733,7 +59808,7 @@
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="6"/>
       <c r="C41" s="75" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D41" s="75"/>
       <c r="E41" s="75"/>
@@ -59776,7 +59851,7 @@
     <row r="43" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="76" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C44" s="76"/>
       <c r="D44" s="76"/>
@@ -59788,7 +59863,7 @@
       <c r="J44" s="76"/>
       <c r="K44" s="76"/>
       <c r="L44" s="77" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M44" s="77"/>
       <c r="N44" s="77"/>
@@ -59798,7 +59873,7 @@
       <c r="R44" s="77"/>
       <c r="S44" s="77"/>
       <c r="U44" s="76" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="V44" s="76"/>
       <c r="W44" s="76"/>
@@ -59811,7 +59886,7 @@
       <c r="AD44" s="76"/>
       <c r="AE44" s="76"/>
       <c r="AF44" s="77" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AG44" s="77"/>
       <c r="AH44" s="77"/>
@@ -59824,7 +59899,7 @@
     <row r="45" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="46" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="78" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C46" s="78"/>
       <c r="D46" s="78"/>
@@ -59844,7 +59919,7 @@
       <c r="R46" s="78"/>
       <c r="S46" s="78"/>
       <c r="T46" s="79" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="U46" s="79"/>
       <c r="V46" s="79"/>
@@ -59908,7 +59983,7 @@
     </row>
     <row r="88" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B88" s="80" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C88" s="80"/>
       <c r="D88" s="80"/>
@@ -59951,7 +60026,7 @@
     <row r="89" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="90" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B90" s="81" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="C90" s="81"/>
       <c r="D90" s="81"/>
@@ -59961,7 +60036,7 @@
       <c r="H90" s="81"/>
       <c r="I90" s="81"/>
       <c r="J90" s="81" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="K90" s="81"/>
       <c r="L90" s="81"/>
@@ -59969,7 +60044,7 @@
       <c r="N90" s="81"/>
       <c r="O90" s="81"/>
       <c r="P90" s="81" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="Q90" s="81"/>
       <c r="R90" s="81"/>
@@ -59977,7 +60052,7 @@
       <c r="T90" s="81"/>
       <c r="U90" s="81"/>
       <c r="V90" s="81" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="W90" s="81"/>
       <c r="X90" s="81"/>
@@ -59985,7 +60060,7 @@
       <c r="Z90" s="81"/>
       <c r="AA90" s="81"/>
       <c r="AB90" s="81" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="AC90" s="81"/>
       <c r="AD90" s="81"/>
@@ -59993,7 +60068,7 @@
       <c r="AF90" s="81"/>
       <c r="AG90" s="81"/>
       <c r="AH90" s="81" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="AI90" s="81"/>
       <c r="AJ90" s="81"/>
@@ -60003,7 +60078,7 @@
     </row>
     <row r="91" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B91" s="82" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C91" s="82"/>
       <c r="D91" s="82"/>
@@ -60045,7 +60120,7 @@
     </row>
     <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B92" s="82" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C92" s="82"/>
       <c r="D92" s="82"/>
@@ -60087,7 +60162,7 @@
     </row>
     <row r="93" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B93" s="82" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C93" s="82"/>
       <c r="D93" s="82"/>
@@ -60129,7 +60204,7 @@
     </row>
     <row r="94" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B94" s="82" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C94" s="82"/>
       <c r="D94" s="82"/>
@@ -60171,7 +60246,7 @@
     </row>
     <row r="95" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="82" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C95" s="82"/>
       <c r="D95" s="82"/>
@@ -60213,7 +60288,7 @@
     </row>
     <row r="96" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B96" s="82" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C96" s="82"/>
       <c r="D96" s="82"/>
@@ -60473,7 +60548,7 @@
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2"/>
       <c r="C2" s="28" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
@@ -60503,7 +60578,7 @@
       <c r="AC2" s="2"/>
       <c r="AD2" s="2"/>
       <c r="AE2" s="29" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AF2" s="29"/>
       <c r="AG2" s="29"/>
@@ -60517,7 +60592,7 @@
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="2"/>
       <c r="C3" s="30" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="30"/>
@@ -60544,7 +60619,7 @@
       <c r="Z3" s="30"/>
       <c r="AA3" s="30"/>
       <c r="AB3" s="31" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="AC3" s="31"/>
       <c r="AD3" s="31"/>
@@ -60561,7 +60636,7 @@
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="2"/>
       <c r="C4" s="32" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
@@ -60683,7 +60758,7 @@
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
@@ -60707,7 +60782,7 @@
       <c r="U8" s="33"/>
       <c r="V8" s="33"/>
       <c r="X8" s="33" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="Y8" s="33"/>
       <c r="Z8" s="33"/>
@@ -60716,7 +60791,7 @@
       <c r="AC8" s="33"/>
       <c r="AD8" s="33"/>
       <c r="AF8" s="33" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="AG8" s="33"/>
       <c r="AH8" s="33"/>
@@ -60728,7 +60803,7 @@
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="85" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -60742,7 +60817,7 @@
       <c r="L9" s="85"/>
       <c r="M9" s="85"/>
       <c r="O9" s="85" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="P9" s="85"/>
       <c r="Q9" s="85"/>
@@ -60773,7 +60848,7 @@
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="6"/>
       <c r="C11" s="37" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="37"/>
@@ -60814,7 +60889,7 @@
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="88" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C12" s="88"/>
       <c r="D12" s="88"/>
@@ -60822,7 +60897,7 @@
       <c r="F12" s="88"/>
       <c r="G12" s="88"/>
       <c r="I12" s="88" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J12" s="88"/>
       <c r="K12" s="88"/>
@@ -60830,7 +60905,7 @@
       <c r="M12" s="88"/>
       <c r="N12" s="88"/>
       <c r="P12" s="88" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="Q12" s="88"/>
       <c r="R12" s="88"/>
@@ -60838,21 +60913,21 @@
       <c r="T12" s="88"/>
       <c r="U12" s="88"/>
       <c r="W12" s="88" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="X12" s="88"/>
       <c r="Y12" s="88"/>
       <c r="Z12" s="88"/>
       <c r="AA12" s="88"/>
       <c r="AC12" s="88" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="AD12" s="88"/>
       <c r="AE12" s="88"/>
       <c r="AF12" s="88"/>
       <c r="AG12" s="88"/>
       <c r="AI12" s="88" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="AJ12" s="88"/>
       <c r="AK12" s="88"/>
@@ -60914,7 +60989,7 @@
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="91" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C14" s="91"/>
       <c r="D14" s="91"/>
@@ -60922,7 +60997,7 @@
       <c r="F14" s="91"/>
       <c r="G14" s="91"/>
       <c r="I14" s="91" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J14" s="91"/>
       <c r="K14" s="91"/>
@@ -60930,7 +61005,7 @@
       <c r="M14" s="91"/>
       <c r="N14" s="91"/>
       <c r="P14" s="91" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Q14" s="91"/>
       <c r="R14" s="91"/>
@@ -60938,21 +61013,21 @@
       <c r="T14" s="91"/>
       <c r="U14" s="91"/>
       <c r="W14" s="91" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="X14" s="91"/>
       <c r="Y14" s="91"/>
       <c r="Z14" s="91"/>
       <c r="AA14" s="91"/>
       <c r="AC14" s="91" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="AD14" s="91"/>
       <c r="AE14" s="91"/>
       <c r="AF14" s="91"/>
       <c r="AG14" s="91"/>
       <c r="AI14" s="91" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="AJ14" s="91"/>
       <c r="AK14" s="91"/>
@@ -60963,7 +61038,7 @@
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6"/>
       <c r="C16" s="37" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D16" s="37"/>
       <c r="E16" s="37"/>
@@ -61004,34 +61079,34 @@
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="52" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
       <c r="F17" s="52" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G17" s="52"/>
       <c r="H17" s="52"/>
       <c r="I17" s="52"/>
       <c r="J17" s="52"/>
       <c r="K17" s="52" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="L17" s="52"/>
       <c r="M17" s="52"/>
       <c r="N17" s="52"/>
       <c r="O17" s="52"/>
       <c r="P17" s="52" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Q17" s="52"/>
       <c r="R17" s="52"/>
       <c r="S17" s="52"/>
       <c r="T17" s="52"/>
       <c r="U17" s="52" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="V17" s="52"/>
       <c r="W17" s="52"/>
@@ -61039,7 +61114,7 @@
       <c r="Y17" s="52"/>
       <c r="Z17" s="52"/>
       <c r="AA17" s="52" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="AB17" s="52"/>
       <c r="AC17" s="52"/>
@@ -61047,7 +61122,7 @@
       <c r="AE17" s="52"/>
       <c r="AF17" s="52"/>
       <c r="AG17" s="52" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="AH17" s="52"/>
       <c r="AI17" s="52"/>
@@ -61058,7 +61133,7 @@
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="92" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="C18" s="92"/>
       <c r="D18" s="92"/>
@@ -61118,7 +61193,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="92" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C19" s="92"/>
       <c r="D19" s="92"/>
@@ -61178,7 +61253,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="92" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C20" s="92"/>
       <c r="D20" s="92"/>
@@ -61238,7 +61313,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="92" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C21" s="92"/>
       <c r="D21" s="92"/>
@@ -61298,7 +61373,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="92" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C22" s="92"/>
       <c r="D22" s="92"/>
@@ -61358,7 +61433,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="96" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C23" s="96"/>
       <c r="D23" s="96"/>
@@ -61419,7 +61494,7 @@
     <row r="24" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="99" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="C25" s="99"/>
       <c r="D25" s="99"/>
@@ -61496,7 +61571,7 @@
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="6"/>
       <c r="C28" s="37" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D28" s="37"/>
       <c r="E28" s="37"/>
@@ -61509,7 +61584,7 @@
       <c r="L28" s="37"/>
       <c r="M28" s="37"/>
       <c r="N28" s="38" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="O28" s="38"/>
       <c r="P28" s="38"/>
@@ -61539,7 +61614,7 @@
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="101" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C29" s="101"/>
       <c r="D29" s="101"/>
@@ -61547,46 +61622,46 @@
       <c r="F29" s="101"/>
       <c r="G29" s="101"/>
       <c r="H29" s="101" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="I29" s="101"/>
       <c r="J29" s="101"/>
       <c r="K29" s="101"/>
       <c r="L29" s="101"/>
       <c r="M29" s="101" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="N29" s="101"/>
       <c r="O29" s="101"/>
       <c r="P29" s="101"/>
       <c r="Q29" s="101"/>
       <c r="R29" s="101" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="S29" s="101"/>
       <c r="T29" s="101"/>
       <c r="U29" s="101"/>
       <c r="V29" s="101" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="W29" s="101"/>
       <c r="X29" s="101"/>
       <c r="Y29" s="101"/>
       <c r="Z29" s="101" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AA29" s="101"/>
       <c r="AB29" s="101"/>
       <c r="AC29" s="101"/>
       <c r="AD29" s="101"/>
       <c r="AE29" s="101" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AF29" s="101"/>
       <c r="AG29" s="101"/>
       <c r="AH29" s="101"/>
       <c r="AI29" s="101" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="AJ29" s="101"/>
       <c r="AK29" s="101"/>
@@ -61595,7 +61670,7 @@
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="102" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C30" s="102"/>
       <c r="D30" s="102"/>
@@ -61713,7 +61788,7 @@
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="102" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C32" s="102"/>
       <c r="D32" s="102"/>
@@ -61772,7 +61847,7 @@
     </row>
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="102" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C33" s="102"/>
       <c r="D33" s="102"/>
@@ -61831,7 +61906,7 @@
     </row>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="102" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C34" s="102"/>
       <c r="D34" s="102"/>
@@ -61890,7 +61965,7 @@
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="102" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C35" s="102"/>
       <c r="D35" s="102"/>
@@ -62008,7 +62083,7 @@
     </row>
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="102" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C37" s="102"/>
       <c r="D37" s="102"/>
@@ -62067,7 +62142,7 @@
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="108" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C38" s="108"/>
       <c r="D38" s="108"/>
@@ -62124,7 +62199,7 @@
     </row>
     <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="112" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C39" s="112"/>
       <c r="D39" s="112"/>
@@ -62169,7 +62244,7 @@
     <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="60"/>
       <c r="C42" s="61" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D42" s="61"/>
       <c r="E42" s="61"/>
@@ -62180,7 +62255,7 @@
       <c r="J42" s="61"/>
       <c r="K42" s="61"/>
       <c r="L42" s="62" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="M42" s="62"/>
       <c r="N42" s="62"/>
@@ -62191,7 +62266,7 @@
       <c r="S42" s="62"/>
       <c r="T42" s="60"/>
       <c r="U42" s="113" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="V42" s="113"/>
       <c r="W42" s="113"/>
@@ -62216,7 +62291,7 @@
     <row r="44" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="33" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C45" s="33"/>
       <c r="D45" s="33"/>
@@ -62228,7 +62303,7 @@
       <c r="J45" s="33"/>
       <c r="K45" s="33"/>
       <c r="M45" s="33" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="N45" s="33"/>
       <c r="O45" s="33"/>
@@ -62240,7 +62315,7 @@
       <c r="U45" s="33"/>
       <c r="V45" s="33"/>
       <c r="X45" s="33" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="Y45" s="33"/>
       <c r="Z45" s="33"/>
@@ -62250,7 +62325,7 @@
       <c r="AD45" s="33"/>
       <c r="AE45" s="33"/>
       <c r="AG45" s="33" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="AH45" s="33"/>
       <c r="AI45" s="33"/>
@@ -62312,7 +62387,7 @@
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="6"/>
       <c r="C48" s="37" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D48" s="37"/>
       <c r="E48" s="37"/>
@@ -62357,7 +62432,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="65" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="E49" s="65"/>
       <c r="F49" s="65"/>
@@ -62370,7 +62445,7 @@
         <v>2</v>
       </c>
       <c r="N49" s="65" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="O49" s="65"/>
       <c r="P49" s="65"/>
@@ -62383,7 +62458,7 @@
         <v>3</v>
       </c>
       <c r="X49" s="65" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="Y49" s="65"/>
       <c r="Z49" s="65"/>
@@ -62396,7 +62471,7 @@
         <v>4</v>
       </c>
       <c r="AH49" s="65" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AI49" s="65"/>
       <c r="AJ49" s="65"/>
@@ -62496,7 +62571,7 @@
         <v>5</v>
       </c>
       <c r="D53" s="115" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E53" s="115"/>
       <c r="F53" s="115"/>
@@ -62519,7 +62594,7 @@
       <c r="W53" s="115"/>
       <c r="X53" s="115"/>
       <c r="Y53" s="116" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="Z53" s="116"/>
       <c r="AA53" s="116"/>
@@ -62533,7 +62608,7 @@
         <v>☐</v>
       </c>
       <c r="C54" s="118" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D54" s="118"/>
       <c r="E54" s="118"/>
@@ -62546,7 +62621,7 @@
         <v>☐</v>
       </c>
       <c r="K54" s="118" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="L54" s="118"/>
       <c r="M54" s="118"/>
@@ -62559,7 +62634,7 @@
         <v>☐</v>
       </c>
       <c r="S54" s="118" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="T54" s="118"/>
       <c r="U54" s="118"/>
@@ -62571,7 +62646,7 @@
         <v>☐</v>
       </c>
       <c r="Z54" s="118" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AA54" s="118"/>
       <c r="AB54" s="118"/>
@@ -62583,7 +62658,7 @@
         <v>☐</v>
       </c>
       <c r="AG54" s="118" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AH54" s="118"/>
       <c r="AI54" s="118"/>
@@ -62598,7 +62673,7 @@
         <v>☐</v>
       </c>
       <c r="C55" s="118" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D55" s="118"/>
       <c r="E55" s="118"/>
@@ -62629,7 +62704,7 @@
     <row r="57" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="6"/>
       <c r="C57" s="37" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D57" s="37"/>
       <c r="E57" s="37"/>
@@ -62648,7 +62723,7 @@
       <c r="R57" s="37"/>
       <c r="S57" s="37"/>
       <c r="T57" s="38" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="U57" s="38"/>
       <c r="V57" s="38"/>
@@ -62732,60 +62807,60 @@
     </row>
     <row r="59" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="129" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C59" s="129"/>
       <c r="D59" s="129"/>
       <c r="E59" s="129"/>
       <c r="F59" s="129" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="G59" s="129"/>
       <c r="H59" s="129"/>
       <c r="I59" s="129"/>
       <c r="J59" s="129" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K59" s="129"/>
       <c r="L59" s="129"/>
       <c r="M59" s="129"/>
       <c r="N59" s="129" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="O59" s="129"/>
       <c r="P59" s="129"/>
       <c r="Q59" s="129"/>
       <c r="R59" s="129" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="S59" s="129"/>
       <c r="T59" s="129"/>
       <c r="U59" s="129"/>
       <c r="V59" s="129" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="W59" s="129"/>
       <c r="X59" s="129"/>
       <c r="Y59" s="129"/>
       <c r="Z59" s="129" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="AA59" s="129"/>
       <c r="AB59" s="129"/>
       <c r="AC59" s="129"/>
       <c r="AD59" s="129" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AE59" s="129"/>
       <c r="AF59" s="129"/>
       <c r="AG59" s="129"/>
       <c r="AH59" s="129" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="AI59" s="129"/>
       <c r="AJ59" s="129"/>
       <c r="AK59" s="129" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="AL59" s="129"/>
       <c r="AM59" s="129"/>
@@ -62793,7 +62868,7 @@
     <row r="60" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="61" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B61" s="130" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="C61" s="130"/>
       <c r="D61" s="130"/>
@@ -62807,14 +62882,14 @@
       <c r="L61" s="130"/>
       <c r="M61" s="130"/>
       <c r="N61" s="131" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="O61" s="131"/>
       <c r="P61" s="131"/>
       <c r="Q61" s="131"/>
       <c r="R61" s="131"/>
       <c r="S61" s="130" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="T61" s="130"/>
       <c r="U61" s="130"/>
@@ -62827,7 +62902,7 @@
       <c r="AB61" s="130"/>
       <c r="AC61" s="130"/>
       <c r="AD61" s="130" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AE61" s="130"/>
       <c r="AF61" s="130"/>
@@ -62844,7 +62919,7 @@
         <v>6</v>
       </c>
       <c r="C62" s="133" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D62" s="133"/>
       <c r="E62" s="133"/>
@@ -62863,7 +62938,7 @@
       <c r="O62" s="134"/>
       <c r="P62" s="134"/>
       <c r="Q62" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R62" s="135"/>
       <c r="S62" s="136" t="str">
@@ -62899,7 +62974,7 @@
         <v>7</v>
       </c>
       <c r="C63" s="133" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D63" s="133"/>
       <c r="E63" s="133"/>
@@ -62918,7 +62993,7 @@
       <c r="O63" s="134"/>
       <c r="P63" s="134"/>
       <c r="Q63" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R63" s="135"/>
       <c r="S63" s="136" t="str">
@@ -62954,7 +63029,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="133" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D64" s="133"/>
       <c r="E64" s="133"/>
@@ -62973,7 +63048,7 @@
       <c r="O64" s="134"/>
       <c r="P64" s="134"/>
       <c r="Q64" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R64" s="135"/>
       <c r="S64" s="136" t="str">
@@ -63009,7 +63084,7 @@
         <v>9</v>
       </c>
       <c r="C65" s="133" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D65" s="133"/>
       <c r="E65" s="133"/>
@@ -63028,7 +63103,7 @@
       <c r="O65" s="134"/>
       <c r="P65" s="134"/>
       <c r="Q65" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R65" s="135"/>
       <c r="S65" s="136" t="str">
@@ -63064,7 +63139,7 @@
         <v>10</v>
       </c>
       <c r="C66" s="133" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D66" s="133"/>
       <c r="E66" s="133"/>
@@ -63083,7 +63158,7 @@
       <c r="O66" s="134"/>
       <c r="P66" s="134"/>
       <c r="Q66" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R66" s="135"/>
       <c r="S66" s="136" t="str">
@@ -63119,7 +63194,7 @@
         <v>11</v>
       </c>
       <c r="C67" s="133" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="D67" s="133"/>
       <c r="E67" s="133"/>
@@ -63138,7 +63213,7 @@
       <c r="O67" s="134"/>
       <c r="P67" s="134"/>
       <c r="Q67" s="135" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R67" s="135"/>
       <c r="S67" s="136" t="str">
@@ -63174,7 +63249,7 @@
         <v>12</v>
       </c>
       <c r="C68" s="137" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D68" s="137"/>
       <c r="E68" s="137"/>
@@ -63193,7 +63268,7 @@
       <c r="O68" s="138"/>
       <c r="P68" s="138"/>
       <c r="Q68" s="139" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R68" s="139"/>
       <c r="S68" s="140"/>
@@ -63222,7 +63297,7 @@
     <row r="70" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="6"/>
       <c r="C70" s="37" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D70" s="37"/>
       <c r="E70" s="37"/>
@@ -63267,7 +63342,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="78" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E71" s="78"/>
       <c r="F71" s="78"/>
@@ -63290,7 +63365,7 @@
         <v>14</v>
       </c>
       <c r="X71" s="78" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="Y71" s="78"/>
       <c r="Z71" s="78"/>
@@ -63474,7 +63549,7 @@
     <row r="77" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="78" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B78" s="76" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C78" s="76"/>
       <c r="D78" s="76"/>
@@ -63486,7 +63561,7 @@
       <c r="J78" s="76"/>
       <c r="K78" s="76"/>
       <c r="L78" s="77" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M78" s="77"/>
       <c r="N78" s="77"/>
@@ -63496,7 +63571,7 @@
       <c r="R78" s="77"/>
       <c r="S78" s="77"/>
       <c r="U78" s="76" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="V78" s="76"/>
       <c r="W78" s="76"/>
@@ -63509,7 +63584,7 @@
       <c r="AD78" s="76"/>
       <c r="AE78" s="76"/>
       <c r="AF78" s="77" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="AG78" s="77"/>
       <c r="AH78" s="77"/>
@@ -63561,7 +63636,7 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="80" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C119" s="80"/>
       <c r="D119" s="80"/>
@@ -63604,7 +63679,7 @@
     <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B120" s="6"/>
       <c r="C120" s="37" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D120" s="37"/>
       <c r="E120" s="37"/>
@@ -63645,21 +63720,21 @@
     </row>
     <row r="121" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B121" s="101" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C121" s="101"/>
       <c r="D121" s="101"/>
       <c r="E121" s="101"/>
       <c r="F121" s="101"/>
       <c r="G121" s="101" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H121" s="101"/>
       <c r="I121" s="101"/>
       <c r="J121" s="101"/>
       <c r="K121" s="101"/>
       <c r="L121" s="101" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M121" s="101"/>
       <c r="N121" s="101"/>
@@ -63667,20 +63742,20 @@
       <c r="P121" s="101"/>
       <c r="Q121" s="101"/>
       <c r="R121" s="101" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="S121" s="101"/>
       <c r="T121" s="101"/>
       <c r="U121" s="101"/>
       <c r="V121" s="101"/>
       <c r="W121" s="101" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="X121" s="101"/>
       <c r="Y121" s="101"/>
       <c r="Z121" s="101"/>
       <c r="AA121" s="101" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AB121" s="101"/>
       <c r="AC121" s="101"/>
@@ -63688,7 +63763,7 @@
       <c r="AE121" s="101"/>
       <c r="AF121" s="101"/>
       <c r="AG121" s="101" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="AH121" s="101"/>
       <c r="AI121" s="101"/>
@@ -64045,7 +64120,7 @@
     <row r="131" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B131" s="6"/>
       <c r="C131" s="37" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D131" s="37"/>
       <c r="E131" s="37"/>
@@ -64087,14 +64162,14 @@
     <row r="132" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="133" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B133" s="101" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C133" s="101"/>
       <c r="D133" s="101"/>
       <c r="E133" s="101"/>
       <c r="F133" s="101"/>
       <c r="G133" s="101" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="H133" s="101"/>
       <c r="I133" s="101"/>
@@ -64103,12 +64178,12 @@
       <c r="L133" s="101"/>
       <c r="M133" s="101"/>
       <c r="N133" s="101" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="O133" s="101"/>
       <c r="P133" s="101"/>
       <c r="Q133" s="101" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="R133" s="101"/>
       <c r="S133" s="101"/>
@@ -64121,7 +64196,7 @@
       <c r="Z133" s="101"/>
       <c r="AA133" s="101"/>
       <c r="AB133" s="101" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AC133" s="101"/>
       <c r="AD133" s="101"/>
@@ -64145,7 +64220,7 @@
       <c r="E134" s="82"/>
       <c r="F134" s="82"/>
       <c r="G134" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H134" s="145"/>
       <c r="I134" s="145"/>
@@ -64190,7 +64265,7 @@
       <c r="E135" s="82"/>
       <c r="F135" s="82"/>
       <c r="G135" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H135" s="145"/>
       <c r="I135" s="145"/>
@@ -64235,7 +64310,7 @@
       <c r="E136" s="82"/>
       <c r="F136" s="82"/>
       <c r="G136" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H136" s="145"/>
       <c r="I136" s="145"/>
@@ -64280,7 +64355,7 @@
       <c r="E137" s="82"/>
       <c r="F137" s="82"/>
       <c r="G137" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H137" s="145"/>
       <c r="I137" s="145"/>
@@ -64325,7 +64400,7 @@
       <c r="E138" s="82"/>
       <c r="F138" s="82"/>
       <c r="G138" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H138" s="145"/>
       <c r="I138" s="145"/>
@@ -64370,7 +64445,7 @@
       <c r="E139" s="82"/>
       <c r="F139" s="82"/>
       <c r="G139" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H139" s="145"/>
       <c r="I139" s="145"/>
@@ -64415,7 +64490,7 @@
       <c r="E140" s="82"/>
       <c r="F140" s="82"/>
       <c r="G140" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H140" s="145"/>
       <c r="I140" s="145"/>
@@ -64460,7 +64535,7 @@
       <c r="E141" s="82"/>
       <c r="F141" s="82"/>
       <c r="G141" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H141" s="145"/>
       <c r="I141" s="145"/>
@@ -64505,7 +64580,7 @@
       <c r="E142" s="82"/>
       <c r="F142" s="82"/>
       <c r="G142" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H142" s="145"/>
       <c r="I142" s="145"/>
@@ -64550,7 +64625,7 @@
       <c r="E143" s="82"/>
       <c r="F143" s="82"/>
       <c r="G143" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H143" s="145"/>
       <c r="I143" s="145"/>
@@ -64595,7 +64670,7 @@
       <c r="E144" s="82"/>
       <c r="F144" s="82"/>
       <c r="G144" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H144" s="145"/>
       <c r="I144" s="145"/>
@@ -64640,7 +64715,7 @@
       <c r="E145" s="82"/>
       <c r="F145" s="82"/>
       <c r="G145" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H145" s="145"/>
       <c r="I145" s="145"/>
@@ -64685,7 +64760,7 @@
       <c r="E146" s="82"/>
       <c r="F146" s="82"/>
       <c r="G146" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H146" s="145"/>
       <c r="I146" s="145"/>
@@ -64730,7 +64805,7 @@
       <c r="E147" s="82"/>
       <c r="F147" s="82"/>
       <c r="G147" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H147" s="145"/>
       <c r="I147" s="145"/>
@@ -64775,7 +64850,7 @@
       <c r="E148" s="82"/>
       <c r="F148" s="82"/>
       <c r="G148" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H148" s="145"/>
       <c r="I148" s="145"/>
@@ -64820,7 +64895,7 @@
       <c r="E149" s="82"/>
       <c r="F149" s="82"/>
       <c r="G149" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H149" s="145"/>
       <c r="I149" s="145"/>
@@ -64865,7 +64940,7 @@
       <c r="E150" s="82"/>
       <c r="F150" s="82"/>
       <c r="G150" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H150" s="145"/>
       <c r="I150" s="145"/>
@@ -64910,7 +64985,7 @@
       <c r="E151" s="82"/>
       <c r="F151" s="82"/>
       <c r="G151" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H151" s="145"/>
       <c r="I151" s="145"/>
@@ -64955,7 +65030,7 @@
       <c r="E152" s="82"/>
       <c r="F152" s="82"/>
       <c r="G152" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H152" s="145"/>
       <c r="I152" s="145"/>
@@ -65000,7 +65075,7 @@
       <c r="E153" s="82"/>
       <c r="F153" s="82"/>
       <c r="G153" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H153" s="145"/>
       <c r="I153" s="145"/>
@@ -65045,7 +65120,7 @@
       <c r="E154" s="82"/>
       <c r="F154" s="82"/>
       <c r="G154" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H154" s="145"/>
       <c r="I154" s="145"/>
@@ -65090,7 +65165,7 @@
       <c r="E155" s="82"/>
       <c r="F155" s="82"/>
       <c r="G155" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H155" s="145"/>
       <c r="I155" s="145"/>
@@ -65135,7 +65210,7 @@
       <c r="E156" s="82"/>
       <c r="F156" s="82"/>
       <c r="G156" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H156" s="145"/>
       <c r="I156" s="145"/>
@@ -65180,7 +65255,7 @@
       <c r="E157" s="82"/>
       <c r="F157" s="82"/>
       <c r="G157" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H157" s="145"/>
       <c r="I157" s="145"/>
@@ -65225,7 +65300,7 @@
       <c r="E158" s="82"/>
       <c r="F158" s="82"/>
       <c r="G158" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H158" s="145"/>
       <c r="I158" s="145"/>
@@ -65270,7 +65345,7 @@
       <c r="E159" s="82"/>
       <c r="F159" s="82"/>
       <c r="G159" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H159" s="145"/>
       <c r="I159" s="145"/>
@@ -65315,7 +65390,7 @@
       <c r="E160" s="82"/>
       <c r="F160" s="82"/>
       <c r="G160" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H160" s="145"/>
       <c r="I160" s="145"/>
@@ -65360,7 +65435,7 @@
       <c r="E161" s="82"/>
       <c r="F161" s="82"/>
       <c r="G161" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H161" s="145"/>
       <c r="I161" s="145"/>
@@ -65405,7 +65480,7 @@
       <c r="E162" s="82"/>
       <c r="F162" s="82"/>
       <c r="G162" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H162" s="145"/>
       <c r="I162" s="145"/>
@@ -65450,7 +65525,7 @@
       <c r="E163" s="82"/>
       <c r="F163" s="82"/>
       <c r="G163" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H163" s="145"/>
       <c r="I163" s="145"/>
@@ -65495,7 +65570,7 @@
       <c r="E164" s="82"/>
       <c r="F164" s="82"/>
       <c r="G164" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H164" s="145"/>
       <c r="I164" s="145"/>
@@ -65540,7 +65615,7 @@
       <c r="E165" s="82"/>
       <c r="F165" s="82"/>
       <c r="G165" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H165" s="145"/>
       <c r="I165" s="145"/>
@@ -65585,7 +65660,7 @@
       <c r="E166" s="82"/>
       <c r="F166" s="82"/>
       <c r="G166" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H166" s="145"/>
       <c r="I166" s="145"/>
@@ -65630,7 +65705,7 @@
       <c r="E167" s="82"/>
       <c r="F167" s="82"/>
       <c r="G167" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H167" s="145"/>
       <c r="I167" s="145"/>
@@ -65675,7 +65750,7 @@
       <c r="E168" s="82"/>
       <c r="F168" s="82"/>
       <c r="G168" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H168" s="145"/>
       <c r="I168" s="145"/>
@@ -65720,7 +65795,7 @@
       <c r="E169" s="82"/>
       <c r="F169" s="82"/>
       <c r="G169" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H169" s="145"/>
       <c r="I169" s="145"/>
@@ -65765,7 +65840,7 @@
       <c r="E170" s="82"/>
       <c r="F170" s="82"/>
       <c r="G170" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H170" s="145"/>
       <c r="I170" s="145"/>
@@ -65810,7 +65885,7 @@
       <c r="E171" s="82"/>
       <c r="F171" s="82"/>
       <c r="G171" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H171" s="145"/>
       <c r="I171" s="145"/>
@@ -65855,7 +65930,7 @@
       <c r="E172" s="82"/>
       <c r="F172" s="82"/>
       <c r="G172" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H172" s="145"/>
       <c r="I172" s="145"/>
@@ -65900,7 +65975,7 @@
       <c r="E173" s="82"/>
       <c r="F173" s="82"/>
       <c r="G173" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H173" s="145"/>
       <c r="I173" s="145"/>
@@ -65945,7 +66020,7 @@
       <c r="E174" s="82"/>
       <c r="F174" s="82"/>
       <c r="G174" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H174" s="145"/>
       <c r="I174" s="145"/>
@@ -65990,7 +66065,7 @@
       <c r="E175" s="82"/>
       <c r="F175" s="82"/>
       <c r="G175" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H175" s="145"/>
       <c r="I175" s="145"/>
@@ -66035,7 +66110,7 @@
       <c r="E176" s="82"/>
       <c r="F176" s="82"/>
       <c r="G176" s="145" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="H176" s="145"/>
       <c r="I176" s="145"/>
@@ -66080,7 +66155,7 @@
       <c r="E177" s="82"/>
       <c r="F177" s="82"/>
       <c r="G177" s="145" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="H177" s="145"/>
       <c r="I177" s="145"/>
@@ -66125,7 +66200,7 @@
       <c r="E178" s="82"/>
       <c r="F178" s="82"/>
       <c r="G178" s="145" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="H178" s="145"/>
       <c r="I178" s="145"/>
@@ -66170,7 +66245,7 @@
       <c r="E179" s="82"/>
       <c r="F179" s="82"/>
       <c r="G179" s="145" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="H179" s="145"/>
       <c r="I179" s="145"/>
@@ -66215,7 +66290,7 @@
       <c r="E180" s="82"/>
       <c r="F180" s="82"/>
       <c r="G180" s="145" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="H180" s="145"/>
       <c r="I180" s="145"/>
@@ -66260,7 +66335,7 @@
       <c r="E181" s="82"/>
       <c r="F181" s="82"/>
       <c r="G181" s="145" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="H181" s="145"/>
       <c r="I181" s="145"/>

--- a/tracker/Travnook_TL_Tracker_Oct2026.xlsx
+++ b/tracker/Travnook_TL_Tracker_Oct2026.xlsx
@@ -3471,7 +3471,9 @@
       <c r="O11" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="16"/>
+      <c r="P11" s="16" t="n">
+        <v>0</v>
+      </c>
       <c r="Q11" s="16" t="n">
         <v>0</v>
       </c>
